--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -453,10 +453,10 @@
         <v>49</v>
       </c>
       <c r="D3">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
